--- a/010-npm_node/02-results/2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx
+++ b/010-npm_node/02-results/2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,18 +437,6 @@
       <c r="L1" t="str">
         <v>11</v>
       </c>
-      <c r="M1" t="str">
-        <v>12</v>
-      </c>
-      <c r="N1" t="str">
-        <v>13</v>
-      </c>
-      <c r="O1" t="str">
-        <v>14</v>
-      </c>
-      <c r="P1" t="str">
-        <v>15</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -487,18 +475,6 @@
       <c r="L2" t="str">
         <v>CONTRACT_FILE</v>
       </c>
-      <c r="M2" t="str">
-        <v>4</v>
-      </c>
-      <c r="N2" t="str">
-        <v>5</v>
-      </c>
-      <c r="O2" t="str">
-        <v>6</v>
-      </c>
-      <c r="P2" t="str">
-        <v>8</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -7876,26 +7852,38 @@
       <c r="A197" t="str">
         <v xml:space="preserve">#17: AMENITY SIGNAGE </v>
       </c>
-      <c r="E197" t="str">
-        <v>2108AC01S</v>
-      </c>
-      <c r="F197" t="str">
-        <v>TAPESTRY (DISCOVERY PHASE III)</v>
+      <c r="B197" t="str">
+        <v>I.</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197" t="str">
+        <v>DOG PARK ID / POLICY - FENCE MOUNT</v>
+      </c>
+      <c r="E197">
+        <v>595</v>
+      </c>
+      <c r="F197">
+        <v>595</v>
       </c>
       <c r="G197" t="str">
-        <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
-      </c>
-      <c r="M197" t="str">
-        <v xml:space="preserve"> X1 @ SMALL POOL)</v>
-      </c>
-      <c r="N197" t="str">
-        <v>ANDRES CONSTRUCTION SERVICES LLC (Construction Manager / General Contractor) 3710 Rawlins Street Suite 1510 |  Dallas, Texas 75219</v>
-      </c>
-      <c r="O197" t="str">
-        <v>Kyle Washington (Project manager)</v>
-      </c>
-      <c r="P197" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+        <v>ANDRES CONSTRUCTION SERVICES LLC (Construction Manager / General Contractor) 3710 Rawlins Street Suite 1510 |  Dallas, Texas 75219</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Kyle Washington (Project manager)</v>
+      </c>
+      <c r="I197" t="str">
+        <v>2108AC01S</v>
+      </c>
+      <c r="J197" t="str">
+        <v>09.23.21 01.19.23 REV 1</v>
+      </c>
+      <c r="K197" t="str">
+        <v>TAPESTRY (DISCOVERY PHASE III)</v>
+      </c>
+      <c r="L197" t="str">
+        <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
     <row r="198">
@@ -7903,19 +7891,19 @@
         <v xml:space="preserve">#17: AMENITY SIGNAGE </v>
       </c>
       <c r="B198" t="str">
-        <v>I.</v>
+        <v>J.</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="str">
-        <v>DOG PARK ID / POLICY - FENCE MOUNT</v>
+        <v>FIRE PIT GUIDELINES PLAQUE</v>
       </c>
       <c r="E198">
-        <v>595</v>
+        <v>110</v>
       </c>
       <c r="F198">
-        <v>595</v>
+        <v>110</v>
       </c>
       <c r="G198" t="str">
         <v>ANDRES CONSTRUCTION SERVICES LLC (Construction Manager / General Contractor) 3710 Rawlins Street Suite 1510 |  Dallas, Texas 75219</v>
@@ -7933,50 +7921,12 @@
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
       </c>
       <c r="L198" t="str">
-        <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v xml:space="preserve">#17: AMENITY SIGNAGE </v>
-      </c>
-      <c r="B199" t="str">
-        <v>J.</v>
-      </c>
-      <c r="C199">
-        <v>1</v>
-      </c>
-      <c r="D199" t="str">
-        <v>FIRE PIT GUIDELINES PLAQUE</v>
-      </c>
-      <c r="E199">
-        <v>110</v>
-      </c>
-      <c r="F199">
-        <v>110</v>
-      </c>
-      <c r="G199" t="str">
-        <v>ANDRES CONSTRUCTION SERVICES LLC (Construction Manager / General Contractor) 3710 Rawlins Street Suite 1510 |  Dallas, Texas 75219</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Kyle Washington (Project manager)</v>
-      </c>
-      <c r="I199" t="str">
-        <v>2108AC01S</v>
-      </c>
-      <c r="J199" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
-      </c>
-      <c r="K199" t="str">
-        <v>TAPESTRY (DISCOVERY PHASE III)</v>
-      </c>
-      <c r="L199" t="str">
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/010-npm_node/02-results/2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx
+++ b/010-npm_node/02-results/2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx
@@ -464,7 +464,7 @@
         <v>CONTACT</v>
       </c>
       <c r="I2" t="str">
-        <v>CONTRACT_NUMBER</v>
+        <v>CONTRACT</v>
       </c>
       <c r="J2" t="str">
         <v>REVISIONS</v>
@@ -476,7 +476,7 @@
         <v>CONTRACT_FILE</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -504,8 +504,9 @@
       <c r="I3" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J3" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J3" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K3" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -514,7 +515,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -542,8 +543,9 @@
       <c r="I4" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J4" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J4" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K4" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -552,7 +554,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -580,8 +582,9 @@
       <c r="I5" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J5" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J5" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K5" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -590,7 +593,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -618,8 +621,9 @@
       <c r="I6" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J6" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J6" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K6" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -628,7 +632,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -656,8 +660,9 @@
       <c r="I7" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J7" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J7" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K7" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -666,7 +671,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -694,8 +699,9 @@
       <c r="I8" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J8" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J8" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K8" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -704,7 +710,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -732,8 +738,9 @@
       <c r="I9" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J9" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J9" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K9" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -742,7 +749,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -770,8 +777,9 @@
       <c r="I10" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J10" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J10" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K10" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -780,7 +788,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -808,8 +816,9 @@
       <c r="I11" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J11" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J11" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K11" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -818,7 +827,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -846,8 +855,9 @@
       <c r="I12" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J12" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J12" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K12" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -856,7 +866,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -884,8 +894,9 @@
       <c r="I13" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J13" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J13" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K13" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -894,7 +905,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" xml:space="preserve">
       <c r="A14" t="str">
         <v>#2: LEASING CENTER - EXTERIOR SIGNAGE</v>
       </c>
@@ -922,8 +933,9 @@
       <c r="I14" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J14" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J14" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K14" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -932,7 +944,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" xml:space="preserve">
       <c r="A15" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -960,8 +972,9 @@
       <c r="I15" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J15" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J15" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K15" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -970,7 +983,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" xml:space="preserve">
       <c r="A16" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -998,8 +1011,9 @@
       <c r="I16" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J16" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J16" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K16" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1008,7 +1022,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" xml:space="preserve">
       <c r="A17" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -1036,8 +1050,9 @@
       <c r="I17" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J17" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J17" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K17" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1046,7 +1061,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" xml:space="preserve">
       <c r="A18" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -1074,8 +1089,9 @@
       <c r="I18" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J18" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J18" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K18" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1084,7 +1100,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" xml:space="preserve">
       <c r="A19" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -1112,8 +1128,9 @@
       <c r="I19" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J19" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J19" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K19" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1122,7 +1139,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -1150,8 +1167,9 @@
       <c r="I20" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J20" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J20" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K20" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1160,7 +1178,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" xml:space="preserve">
       <c r="A21" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -1188,8 +1206,9 @@
       <c r="I21" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J21" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J21" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K21" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1198,7 +1217,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" xml:space="preserve">
       <c r="A22" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -1226,8 +1245,9 @@
       <c r="I22" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J22" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J22" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K22" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1236,7 +1256,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" xml:space="preserve">
       <c r="A23" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -1264,8 +1284,9 @@
       <c r="I23" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J23" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J23" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K23" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1274,7 +1295,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" xml:space="preserve">
       <c r="A24" t="str">
         <v>#3: LEASING CENTER - INTERIOR SIGNAGE</v>
       </c>
@@ -1302,8 +1323,9 @@
       <c r="I24" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J24" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J24" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K24" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1312,7 +1334,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" xml:space="preserve">
       <c r="A25" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1340,8 +1362,9 @@
       <c r="I25" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J25" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J25" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K25" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1350,7 +1373,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" xml:space="preserve">
       <c r="A26" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1378,8 +1401,9 @@
       <c r="I26" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J26" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J26" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K26" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1388,7 +1412,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1416,8 +1440,9 @@
       <c r="I27" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J27" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J27" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K27" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1426,7 +1451,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" xml:space="preserve">
       <c r="A28" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1454,8 +1479,9 @@
       <c r="I28" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J28" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J28" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K28" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1464,7 +1490,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" xml:space="preserve">
       <c r="A29" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1492,8 +1518,9 @@
       <c r="I29" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J29" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J29" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K29" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1502,7 +1529,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" xml:space="preserve">
       <c r="A30" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1530,8 +1557,9 @@
       <c r="I30" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J30" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J30" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K30" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1540,7 +1568,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1568,8 +1596,9 @@
       <c r="I31" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J31" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J31" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K31" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1578,7 +1607,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" xml:space="preserve">
       <c r="A32" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1606,8 +1635,9 @@
       <c r="I32" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J32" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J32" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K32" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1616,7 +1646,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" xml:space="preserve">
       <c r="A33" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1644,8 +1674,9 @@
       <c r="I33" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J33" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J33" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K33" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1654,7 +1685,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" xml:space="preserve">
       <c r="A34" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1682,8 +1713,9 @@
       <c r="I34" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J34" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J34" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K34" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1692,7 +1724,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" xml:space="preserve">
       <c r="A35" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1720,8 +1752,9 @@
       <c r="I35" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J35" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J35" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K35" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1730,7 +1763,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" xml:space="preserve">
       <c r="A36" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1758,8 +1791,9 @@
       <c r="I36" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J36" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K36" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1768,7 +1802,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" xml:space="preserve">
       <c r="A37" t="str">
         <v xml:space="preserve">#4:  FITNESS CENTER </v>
       </c>
@@ -1796,8 +1830,9 @@
       <c r="I37" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J37" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K37" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1806,7 +1841,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
         <v>#5: SITE SIGNAGE</v>
       </c>
@@ -1834,8 +1869,9 @@
       <c r="I38" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J38" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K38" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1844,7 +1880,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
         <v>#5: SITE SIGNAGE</v>
       </c>
@@ -1872,8 +1908,9 @@
       <c r="I39" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J39" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J39" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K39" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1882,7 +1919,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" xml:space="preserve">
       <c r="A40" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - TERRACE LEVEL SIGNAGE </v>
       </c>
@@ -1910,8 +1947,9 @@
       <c r="I40" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J40" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J40" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K40" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1920,7 +1958,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" xml:space="preserve">
       <c r="A41" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - TERRACE LEVEL SIGNAGE </v>
       </c>
@@ -1948,8 +1986,9 @@
       <c r="I41" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J41" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J41" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K41" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1958,7 +1997,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" xml:space="preserve">
       <c r="A42" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - TERRACE LEVEL SIGNAGE </v>
       </c>
@@ -1986,8 +2025,9 @@
       <c r="I42" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J42" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J42" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K42" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -1996,7 +2036,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - TERRACE LEVEL SIGNAGE </v>
       </c>
@@ -2024,8 +2064,9 @@
       <c r="I43" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J43" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J43" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K43" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2034,7 +2075,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" xml:space="preserve">
       <c r="A44" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - TERRACE LEVEL SIGNAGE </v>
       </c>
@@ -2062,8 +2103,9 @@
       <c r="I44" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J44" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J44" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K44" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2072,7 +2114,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" xml:space="preserve">
       <c r="A45" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - TERRACE LEVEL SIGNAGE </v>
       </c>
@@ -2100,8 +2142,9 @@
       <c r="I45" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J45" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J45" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K45" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2110,7 +2153,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" xml:space="preserve">
       <c r="A46" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - TERRACE LEVEL SIGNAGE </v>
       </c>
@@ -2138,8 +2181,9 @@
       <c r="I46" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J46" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J46" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K46" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2148,7 +2192,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2176,8 +2220,9 @@
       <c r="I47" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J47" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J47" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K47" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2186,7 +2231,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" xml:space="preserve">
       <c r="A48" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2214,8 +2259,9 @@
       <c r="I48" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J48" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J48" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K48" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2224,7 +2270,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" xml:space="preserve">
       <c r="A49" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2252,8 +2298,9 @@
       <c r="I49" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J49" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J49" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K49" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2262,7 +2309,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" xml:space="preserve">
       <c r="A50" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2290,8 +2337,9 @@
       <c r="I50" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J50" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J50" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K50" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2300,7 +2348,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" xml:space="preserve">
       <c r="A51" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2328,8 +2376,9 @@
       <c r="I51" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J51" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J51" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K51" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2338,7 +2387,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" xml:space="preserve">
       <c r="A52" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2366,8 +2415,9 @@
       <c r="I52" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J52" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J52" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K52" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2376,7 +2426,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" xml:space="preserve">
       <c r="A53" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2404,8 +2454,9 @@
       <c r="I53" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J53" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J53" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K53" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2414,7 +2465,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" xml:space="preserve">
       <c r="A54" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2442,8 +2493,9 @@
       <c r="I54" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J54" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J54" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K54" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2452,7 +2504,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" xml:space="preserve">
       <c r="A55" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2480,8 +2532,9 @@
       <c r="I55" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J55" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J55" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K55" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2490,7 +2543,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" xml:space="preserve">
       <c r="A56" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2518,8 +2571,9 @@
       <c r="I56" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J56" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J56" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K56" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2528,7 +2582,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" xml:space="preserve">
       <c r="A57" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2556,8 +2610,9 @@
       <c r="I57" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J57" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J57" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K57" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2566,7 +2621,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" xml:space="preserve">
       <c r="A58" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2594,8 +2649,9 @@
       <c r="I58" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J58" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J58" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K58" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2604,7 +2660,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" xml:space="preserve">
       <c r="A59" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2632,8 +2688,9 @@
       <c r="I59" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J59" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J59" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K59" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2642,7 +2699,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" xml:space="preserve">
       <c r="A60" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2670,8 +2727,9 @@
       <c r="I60" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J60" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J60" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K60" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2680,7 +2738,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" xml:space="preserve">
       <c r="A61" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2708,8 +2766,9 @@
       <c r="I61" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J61" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K61" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2718,7 +2777,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" xml:space="preserve">
       <c r="A62" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2746,8 +2805,9 @@
       <c r="I62" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J62" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J62" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K62" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2756,7 +2816,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" xml:space="preserve">
       <c r="A63" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2784,8 +2844,9 @@
       <c r="I63" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J63" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J63" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K63" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2794,7 +2855,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" xml:space="preserve">
       <c r="A64" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2822,8 +2883,9 @@
       <c r="I64" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J64" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J64" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K64" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2832,7 +2894,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" xml:space="preserve">
       <c r="A65" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL ONE SIGNAGE </v>
       </c>
@@ -2860,8 +2922,9 @@
       <c r="I65" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J65" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J65" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K65" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2870,7 +2933,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" xml:space="preserve">
       <c r="A66" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -2898,8 +2961,9 @@
       <c r="I66" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J66" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K66" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2908,7 +2972,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" xml:space="preserve">
       <c r="A67" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -2936,8 +3000,9 @@
       <c r="I67" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J67" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J67" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K67" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2946,7 +3011,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" xml:space="preserve">
       <c r="A68" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -2974,8 +3039,9 @@
       <c r="I68" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J68" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J68" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K68" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -2984,7 +3050,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" xml:space="preserve">
       <c r="A69" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -3012,8 +3078,9 @@
       <c r="I69" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J69" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J69" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K69" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3022,7 +3089,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" xml:space="preserve">
       <c r="A70" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -3050,8 +3117,9 @@
       <c r="I70" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J70" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J70" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K70" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3060,7 +3128,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" xml:space="preserve">
       <c r="A71" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -3088,8 +3156,9 @@
       <c r="I71" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J71" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J71" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K71" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3098,7 +3167,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" xml:space="preserve">
       <c r="A72" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -3126,8 +3195,9 @@
       <c r="I72" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J72" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J72" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K72" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3136,7 +3206,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" xml:space="preserve">
       <c r="A73" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -3164,8 +3234,9 @@
       <c r="I73" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J73" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J73" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K73" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3174,7 +3245,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" xml:space="preserve">
       <c r="A74" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -3202,8 +3273,9 @@
       <c r="I74" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J74" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J74" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K74" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3212,7 +3284,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" xml:space="preserve">
       <c r="A75" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -3240,8 +3312,9 @@
       <c r="I75" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J75" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J75" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K75" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3250,7 +3323,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" xml:space="preserve">
       <c r="A76" t="str">
         <v>#8: PARKING GARAGE - LEVEL TWO SIGNAGE</v>
       </c>
@@ -3278,8 +3351,9 @@
       <c r="I76" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J76" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J76" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K76" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3288,7 +3362,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" xml:space="preserve">
       <c r="A77" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3316,8 +3390,9 @@
       <c r="I77" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J77" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J77" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K77" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3326,7 +3401,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" xml:space="preserve">
       <c r="A78" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3354,8 +3429,9 @@
       <c r="I78" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J78" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J78" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K78" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3364,7 +3440,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" xml:space="preserve">
       <c r="A79" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3392,8 +3468,9 @@
       <c r="I79" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J79" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K79" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3402,7 +3479,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" xml:space="preserve">
       <c r="A80" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3430,8 +3507,9 @@
       <c r="I80" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J80" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K80" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3440,7 +3518,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" xml:space="preserve">
       <c r="A81" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3468,8 +3546,9 @@
       <c r="I81" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J81" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K81" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3478,7 +3557,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" xml:space="preserve">
       <c r="A82" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3506,8 +3585,9 @@
       <c r="I82" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J82" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K82" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3516,7 +3596,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" xml:space="preserve">
       <c r="A83" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3544,8 +3624,9 @@
       <c r="I83" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J83" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K83" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3554,7 +3635,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" xml:space="preserve">
       <c r="A84" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3582,8 +3663,9 @@
       <c r="I84" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J84" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K84" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3592,7 +3674,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" xml:space="preserve">
       <c r="A85" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3620,8 +3702,9 @@
       <c r="I85" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J85" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J85" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K85" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3630,7 +3713,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" xml:space="preserve">
       <c r="A86" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3658,8 +3741,9 @@
       <c r="I86" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J86" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J86" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K86" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3668,7 +3752,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" xml:space="preserve">
       <c r="A87" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL THREE SIGNAGE </v>
       </c>
@@ -3696,8 +3780,9 @@
       <c r="I87" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J87" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J87" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K87" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3706,7 +3791,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" xml:space="preserve">
       <c r="A88" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -3734,8 +3819,9 @@
       <c r="I88" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J88" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J88" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K88" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3744,7 +3830,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" xml:space="preserve">
       <c r="A89" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -3772,8 +3858,9 @@
       <c r="I89" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J89" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J89" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K89" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3782,7 +3869,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" xml:space="preserve">
       <c r="A90" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -3810,8 +3897,9 @@
       <c r="I90" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J90" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J90" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K90" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3820,7 +3908,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" xml:space="preserve">
       <c r="A91" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -3848,8 +3936,9 @@
       <c r="I91" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J91" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J91" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K91" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3858,7 +3947,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" xml:space="preserve">
       <c r="A92" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -3886,8 +3975,9 @@
       <c r="I92" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J92" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J92" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K92" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3896,7 +3986,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" xml:space="preserve">
       <c r="A93" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -3924,8 +4014,9 @@
       <c r="I93" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J93" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J93" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K93" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3934,7 +4025,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" xml:space="preserve">
       <c r="A94" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -3962,8 +4053,9 @@
       <c r="I94" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J94" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J94" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K94" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -3972,7 +4064,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" xml:space="preserve">
       <c r="A95" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -4000,8 +4092,9 @@
       <c r="I95" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J95" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J95" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K95" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4010,7 +4103,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" xml:space="preserve">
       <c r="A96" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -4038,8 +4131,9 @@
       <c r="I96" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J96" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J96" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K96" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4048,7 +4142,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" xml:space="preserve">
       <c r="A97" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -4076,8 +4170,9 @@
       <c r="I97" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J97" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J97" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K97" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4086,7 +4181,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" xml:space="preserve">
       <c r="A98" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL FOUR SIGNAGE  </v>
       </c>
@@ -4114,8 +4209,9 @@
       <c r="I98" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J98" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J98" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K98" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4124,7 +4220,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" xml:space="preserve">
       <c r="A99" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL FIVE SIGNAGE </v>
       </c>
@@ -4152,8 +4248,9 @@
       <c r="I99" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J99" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J99" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K99" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4162,7 +4259,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" xml:space="preserve">
       <c r="A100" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL FIVE SIGNAGE </v>
       </c>
@@ -4190,8 +4287,9 @@
       <c r="I100" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J100" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J100" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K100" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4200,7 +4298,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" xml:space="preserve">
       <c r="A101" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL FIVE SIGNAGE </v>
       </c>
@@ -4228,8 +4326,9 @@
       <c r="I101" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J101" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J101" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K101" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4238,7 +4337,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" xml:space="preserve">
       <c r="A102" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL FIVE SIGNAGE </v>
       </c>
@@ -4266,8 +4365,9 @@
       <c r="I102" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J102" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J102" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K102" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4276,7 +4376,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" xml:space="preserve">
       <c r="A103" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL FIVE SIGNAGE </v>
       </c>
@@ -4304,8 +4404,9 @@
       <c r="I103" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J103" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J103" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K103" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4314,7 +4415,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" xml:space="preserve">
       <c r="A104" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL FIVE SIGNAGE </v>
       </c>
@@ -4342,8 +4443,9 @@
       <c r="I104" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J104" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J104" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K104" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4352,7 +4454,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" xml:space="preserve">
       <c r="A105" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL SIX SIGNAGE </v>
       </c>
@@ -4380,8 +4482,9 @@
       <c r="I105" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J105" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J105" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K105" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4390,7 +4493,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" xml:space="preserve">
       <c r="A106" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL SIX SIGNAGE </v>
       </c>
@@ -4418,8 +4521,9 @@
       <c r="I106" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J106" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J106" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K106" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4428,7 +4532,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" xml:space="preserve">
       <c r="A107" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL SIX SIGNAGE </v>
       </c>
@@ -4456,8 +4560,9 @@
       <c r="I107" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J107" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J107" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K107" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4466,7 +4571,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" xml:space="preserve">
       <c r="A108" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL SIX SIGNAGE </v>
       </c>
@@ -4494,8 +4599,9 @@
       <c r="I108" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J108" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J108" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K108" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4504,7 +4610,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" xml:space="preserve">
       <c r="A109" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL SIX SIGNAGE </v>
       </c>
@@ -4532,8 +4638,9 @@
       <c r="I109" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J109" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J109" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K109" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4542,7 +4649,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" xml:space="preserve">
       <c r="A110" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL SIX SIGNAGE </v>
       </c>
@@ -4570,8 +4677,9 @@
       <c r="I110" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J110" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J110" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K110" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4580,7 +4688,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" xml:space="preserve">
       <c r="A111" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL SIX SIGNAGE </v>
       </c>
@@ -4608,8 +4716,9 @@
       <c r="I111" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J111" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J111" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K111" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4618,7 +4727,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" xml:space="preserve">
       <c r="A112" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4646,8 +4755,9 @@
       <c r="I112" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J112" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J112" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K112" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4656,7 +4766,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" xml:space="preserve">
       <c r="A113" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4684,8 +4794,9 @@
       <c r="I113" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J113" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J113" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K113" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4694,7 +4805,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" xml:space="preserve">
       <c r="A114" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4722,8 +4833,9 @@
       <c r="I114" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J114" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J114" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K114" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4732,7 +4844,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" xml:space="preserve">
       <c r="A115" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4760,8 +4872,9 @@
       <c r="I115" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J115" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J115" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K115" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4770,7 +4883,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" xml:space="preserve">
       <c r="A116" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4798,8 +4911,9 @@
       <c r="I116" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J116" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J116" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K116" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4808,7 +4922,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" xml:space="preserve">
       <c r="A117" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4836,8 +4950,9 @@
       <c r="I117" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J117" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J117" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K117" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4846,7 +4961,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" xml:space="preserve">
       <c r="A118" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4874,8 +4989,9 @@
       <c r="I118" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J118" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J118" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K118" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4884,7 +5000,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" xml:space="preserve">
       <c r="A119" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4912,8 +5028,9 @@
       <c r="I119" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J119" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J119" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K119" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4922,7 +5039,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" xml:space="preserve">
       <c r="A120" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4950,8 +5067,9 @@
       <c r="I120" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J120" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J120" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K120" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4960,7 +5078,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" xml:space="preserve">
       <c r="A121" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -4988,8 +5106,9 @@
       <c r="I121" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J121" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J121" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K121" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -4998,7 +5117,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" xml:space="preserve">
       <c r="A122" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5026,8 +5145,9 @@
       <c r="I122" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J122" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J122" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K122" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5036,7 +5156,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" xml:space="preserve">
       <c r="A123" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5064,8 +5184,9 @@
       <c r="I123" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J123" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J123" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K123" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5074,7 +5195,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" xml:space="preserve">
       <c r="A124" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5102,8 +5223,9 @@
       <c r="I124" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J124" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J124" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K124" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5112,7 +5234,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" xml:space="preserve">
       <c r="A125" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5140,8 +5262,9 @@
       <c r="I125" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J125" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J125" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K125" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5150,7 +5273,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" xml:space="preserve">
       <c r="A126" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5178,8 +5301,9 @@
       <c r="I126" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J126" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J126" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K126" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5188,7 +5312,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" xml:space="preserve">
       <c r="A127" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5216,8 +5340,9 @@
       <c r="I127" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J127" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J127" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K127" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5226,7 +5351,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" xml:space="preserve">
       <c r="A128" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5254,8 +5379,9 @@
       <c r="I128" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J128" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J128" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K128" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5264,7 +5390,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" xml:space="preserve">
       <c r="A129" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5292,8 +5418,9 @@
       <c r="I129" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J129" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J129" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K129" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5302,7 +5429,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" xml:space="preserve">
       <c r="A130" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5330,8 +5457,9 @@
       <c r="I130" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J130" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J130" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K130" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5340,7 +5468,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" xml:space="preserve">
       <c r="A131" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5368,8 +5496,9 @@
       <c r="I131" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J131" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J131" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K131" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5378,7 +5507,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" xml:space="preserve">
       <c r="A132" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5406,8 +5535,9 @@
       <c r="I132" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J132" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J132" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K132" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5416,7 +5546,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" xml:space="preserve">
       <c r="A133" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5444,8 +5574,9 @@
       <c r="I133" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J133" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J133" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K133" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5454,7 +5585,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" xml:space="preserve">
       <c r="A134" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5482,8 +5613,9 @@
       <c r="I134" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J134" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J134" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K134" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5492,7 +5624,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" xml:space="preserve">
       <c r="A135" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5520,8 +5652,9 @@
       <c r="I135" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J135" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J135" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K135" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5530,7 +5663,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" xml:space="preserve">
       <c r="A136" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5558,8 +5691,9 @@
       <c r="I136" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J136" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J136" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K136" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5568,7 +5702,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" xml:space="preserve">
       <c r="A137" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5596,8 +5730,9 @@
       <c r="I137" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J137" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J137" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K137" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5606,7 +5741,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" xml:space="preserve">
       <c r="A138" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5634,8 +5769,9 @@
       <c r="I138" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J138" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J138" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K138" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5644,7 +5780,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" xml:space="preserve">
       <c r="A139" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5672,8 +5808,9 @@
       <c r="I139" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J139" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J139" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K139" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5682,7 +5819,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" xml:space="preserve">
       <c r="A140" t="str">
         <v xml:space="preserve">#13: BUILDING - LEVEL ONE SIGNAGE </v>
       </c>
@@ -5710,8 +5847,9 @@
       <c r="I140" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J140" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J140" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K140" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5720,7 +5858,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" xml:space="preserve">
       <c r="A141" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -5748,8 +5886,9 @@
       <c r="I141" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J141" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J141" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K141" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5758,7 +5897,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" xml:space="preserve">
       <c r="A142" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -5786,8 +5925,9 @@
       <c r="I142" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J142" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J142" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K142" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5796,7 +5936,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" xml:space="preserve">
       <c r="A143" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -5824,8 +5964,9 @@
       <c r="I143" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J143" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J143" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K143" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5834,7 +5975,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" xml:space="preserve">
       <c r="A144" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -5862,8 +6003,9 @@
       <c r="I144" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J144" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J144" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K144" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5872,7 +6014,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" xml:space="preserve">
       <c r="A145" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -5900,8 +6042,9 @@
       <c r="I145" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J145" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J145" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K145" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5910,7 +6053,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" xml:space="preserve">
       <c r="A146" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -5938,8 +6081,9 @@
       <c r="I146" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J146" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J146" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K146" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5948,7 +6092,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" xml:space="preserve">
       <c r="A147" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -5976,8 +6120,9 @@
       <c r="I147" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J147" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J147" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K147" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -5986,7 +6131,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" xml:space="preserve">
       <c r="A148" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -6014,8 +6159,9 @@
       <c r="I148" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J148" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J148" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K148" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6024,7 +6170,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" xml:space="preserve">
       <c r="A149" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -6052,8 +6198,9 @@
       <c r="I149" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J149" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J149" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K149" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6062,7 +6209,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" xml:space="preserve">
       <c r="A150" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -6090,8 +6237,9 @@
       <c r="I150" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J150" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J150" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K150" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6100,7 +6248,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" xml:space="preserve">
       <c r="A151" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -6128,8 +6276,9 @@
       <c r="I151" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J151" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J151" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K151" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6138,7 +6287,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" xml:space="preserve">
       <c r="A152" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -6166,8 +6315,9 @@
       <c r="I152" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J152" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J152" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K152" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6176,7 +6326,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" xml:space="preserve">
       <c r="A153" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -6204,8 +6354,9 @@
       <c r="I153" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J153" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J153" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K153" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6214,7 +6365,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" xml:space="preserve">
       <c r="A154" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -6242,8 +6393,9 @@
       <c r="I154" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J154" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J154" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K154" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6252,7 +6404,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" xml:space="preserve">
       <c r="A155" t="str">
         <v xml:space="preserve">#14: BUILDING - LEVEL TWO SIGNAGE </v>
       </c>
@@ -6280,8 +6432,9 @@
       <c r="I155" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J155" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J155" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K155" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6290,7 +6443,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" xml:space="preserve">
       <c r="A156" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE </v>
       </c>
@@ -6318,8 +6471,9 @@
       <c r="I156" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J156" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J156" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K156" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6328,7 +6482,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" xml:space="preserve">
       <c r="A157" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE </v>
       </c>
@@ -6356,8 +6510,9 @@
       <c r="I157" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J157" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J157" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K157" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6366,7 +6521,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" xml:space="preserve">
       <c r="A158" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE </v>
       </c>
@@ -6394,8 +6549,9 @@
       <c r="I158" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J158" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J158" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K158" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6404,7 +6560,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" xml:space="preserve">
       <c r="A159" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6432,8 +6588,9 @@
       <c r="I159" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J159" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J159" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K159" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6442,7 +6599,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" xml:space="preserve">
       <c r="A160" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6470,8 +6627,9 @@
       <c r="I160" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J160" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J160" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K160" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6480,7 +6638,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" xml:space="preserve">
       <c r="A161" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6508,8 +6666,9 @@
       <c r="I161" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J161" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J161" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K161" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6518,7 +6677,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" xml:space="preserve">
       <c r="A162" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6546,8 +6705,9 @@
       <c r="I162" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J162" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J162" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K162" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6556,7 +6716,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" xml:space="preserve">
       <c r="A163" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6584,8 +6744,9 @@
       <c r="I163" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J163" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J163" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K163" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6594,7 +6755,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" xml:space="preserve">
       <c r="A164" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6622,8 +6783,9 @@
       <c r="I164" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J164" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J164" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K164" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6632,7 +6794,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" xml:space="preserve">
       <c r="A165" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6660,8 +6822,9 @@
       <c r="I165" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J165" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J165" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K165" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6670,7 +6833,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" xml:space="preserve">
       <c r="A166" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6698,8 +6861,9 @@
       <c r="I166" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J166" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J166" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K166" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6708,7 +6872,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" xml:space="preserve">
       <c r="A167" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6736,8 +6900,9 @@
       <c r="I167" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J167" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J167" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K167" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6746,7 +6911,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" xml:space="preserve">
       <c r="A168" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6774,8 +6939,9 @@
       <c r="I168" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J168" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J168" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K168" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6784,7 +6950,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" xml:space="preserve">
       <c r="A169" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6812,8 +6978,9 @@
       <c r="I169" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J169" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J169" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K169" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6822,7 +6989,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" xml:space="preserve">
       <c r="A170" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6850,8 +7017,9 @@
       <c r="I170" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J170" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J170" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K170" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6860,7 +7028,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" xml:space="preserve">
       <c r="A171" t="str">
         <v xml:space="preserve">#15: BUILDING - LEVEL THREE SIGNAGE  </v>
       </c>
@@ -6888,8 +7056,9 @@
       <c r="I171" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J171" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J171" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K171" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6898,7 +7067,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" xml:space="preserve">
       <c r="A172" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -6926,8 +7095,9 @@
       <c r="I172" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J172" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J172" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K172" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6936,7 +7106,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" xml:space="preserve">
       <c r="A173" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -6964,8 +7134,9 @@
       <c r="I173" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J173" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J173" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K173" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -6974,7 +7145,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" xml:space="preserve">
       <c r="A174" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7002,8 +7173,9 @@
       <c r="I174" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J174" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J174" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K174" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7012,7 +7184,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" xml:space="preserve">
       <c r="A175" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7040,8 +7212,9 @@
       <c r="I175" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J175" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J175" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K175" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7050,7 +7223,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" xml:space="preserve">
       <c r="A176" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7078,8 +7251,9 @@
       <c r="I176" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J176" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J176" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K176" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7088,7 +7262,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" xml:space="preserve">
       <c r="A177" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7116,8 +7290,9 @@
       <c r="I177" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J177" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J177" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K177" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7126,7 +7301,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" xml:space="preserve">
       <c r="A178" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7154,8 +7329,9 @@
       <c r="I178" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J178" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J178" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K178" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7164,7 +7340,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" xml:space="preserve">
       <c r="A179" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7192,8 +7368,9 @@
       <c r="I179" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J179" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J179" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K179" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7202,7 +7379,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" xml:space="preserve">
       <c r="A180" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7230,8 +7407,9 @@
       <c r="I180" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J180" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J180" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K180" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7240,7 +7418,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" xml:space="preserve">
       <c r="A181" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7268,8 +7446,9 @@
       <c r="I181" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J181" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J181" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K181" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7278,7 +7457,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" xml:space="preserve">
       <c r="A182" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7306,8 +7485,9 @@
       <c r="I182" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J182" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J182" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K182" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7316,7 +7496,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" xml:space="preserve">
       <c r="A183" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7344,8 +7524,9 @@
       <c r="I183" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J183" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J183" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K183" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7354,7 +7535,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" xml:space="preserve">
       <c r="A184" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7382,8 +7563,9 @@
       <c r="I184" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J184" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J184" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K184" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7392,7 +7574,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" xml:space="preserve">
       <c r="A185" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7420,8 +7602,9 @@
       <c r="I185" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J185" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J185" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K185" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7430,7 +7613,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" xml:space="preserve">
       <c r="A186" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7458,8 +7641,9 @@
       <c r="I186" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J186" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J186" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K186" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7468,7 +7652,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" xml:space="preserve">
       <c r="A187" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7496,8 +7680,9 @@
       <c r="I187" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J187" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J187" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K187" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7506,7 +7691,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" xml:space="preserve">
       <c r="A188" t="str">
         <v xml:space="preserve">#16: BUILDING - LEVEL FOUR SIGNAGE </v>
       </c>
@@ -7534,8 +7719,9 @@
       <c r="I188" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J188" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J188" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K188" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7544,7 +7730,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" xml:space="preserve">
       <c r="A189" t="str">
         <v>#17: AMENITY SIGNAGE</v>
       </c>
@@ -7572,8 +7758,9 @@
       <c r="I189" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J189" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J189" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K189" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7582,7 +7769,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" xml:space="preserve">
       <c r="A190" t="str">
         <v>#17: AMENITY SIGNAGE</v>
       </c>
@@ -7610,8 +7797,9 @@
       <c r="I190" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J190" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J190" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K190" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7620,7 +7808,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" xml:space="preserve">
       <c r="A191" t="str">
         <v>#17: AMENITY SIGNAGE</v>
       </c>
@@ -7648,8 +7836,9 @@
       <c r="I191" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J191" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J191" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K191" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7658,7 +7847,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" xml:space="preserve">
       <c r="A192" t="str">
         <v>#17: AMENITY SIGNAGE</v>
       </c>
@@ -7686,8 +7875,9 @@
       <c r="I192" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J192" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J192" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K192" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7696,7 +7886,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" xml:space="preserve">
       <c r="A193" t="str">
         <v>#17: AMENITY SIGNAGE</v>
       </c>
@@ -7724,8 +7914,9 @@
       <c r="I193" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J193" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J193" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K193" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7734,7 +7925,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" xml:space="preserve">
       <c r="A194" t="str">
         <v>#17: AMENITY SIGNAGE</v>
       </c>
@@ -7762,8 +7953,9 @@
       <c r="I194" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J194" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J194" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K194" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7772,7 +7964,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" xml:space="preserve">
       <c r="A195" t="str">
         <v xml:space="preserve">#17: AMENITY SIGNAGE </v>
       </c>
@@ -7800,8 +7992,9 @@
       <c r="I195" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J195" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J195" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K195" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7810,7 +8003,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" xml:space="preserve">
       <c r="A196" t="str">
         <v xml:space="preserve">#17: AMENITY SIGNAGE </v>
       </c>
@@ -7838,8 +8031,9 @@
       <c r="I196" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J196" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J196" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K196" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7848,7 +8042,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" xml:space="preserve">
       <c r="A197" t="str">
         <v xml:space="preserve">#17: AMENITY SIGNAGE </v>
       </c>
@@ -7876,8 +8070,9 @@
       <c r="I197" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J197" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J197" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K197" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
@@ -7886,7 +8081,7 @@
         <v>2108AC01S Tapestry (Discovery Phase III) REV 1x.xlsx</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" xml:space="preserve">
       <c r="A198" t="str">
         <v xml:space="preserve">#17: AMENITY SIGNAGE </v>
       </c>
@@ -7914,8 +8109,9 @@
       <c r="I198" t="str">
         <v>2108AC01S</v>
       </c>
-      <c r="J198" t="str">
-        <v>09.23.21 01.19.23 REV 1</v>
+      <c r="J198" t="str" xml:space="preserve">
+        <v xml:space="preserve">09.23.21 01.19.23 REV 1
+</v>
       </c>
       <c r="K198" t="str">
         <v>TAPESTRY (DISCOVERY PHASE III)</v>
